--- a/LeetCode Patterns.xlsx
+++ b/LeetCode Patterns.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sksat\Downloads\leetcode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sksat\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D900737-8A4B-47DD-BB0F-9705821B8D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D56097D-CF3B-45CB-863E-0205535D4F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1465,36 +1465,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1508,34 +1484,49 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1560,6 +1551,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1573,19 +1576,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1708,7 +1710,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1836,15 +1838,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2920,7 +2922,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3178,7 +3180,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3264,7 +3266,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>23</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3350,7 +3352,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3436,7 +3438,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>25</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3522,7 +3524,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>28</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3608,7 +3610,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>29</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3694,7 +3696,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>30</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3780,7 +3782,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>31</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3866,7 +3868,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>32</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3952,7 +3954,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>33</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4038,7 +4040,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>34</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4124,7 +4126,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4210,7 +4212,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>38</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4296,7 +4298,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>39</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4382,7 +4384,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>40</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4468,7 +4470,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>41</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4554,7 +4556,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>42</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4640,7 +4642,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>43</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4726,7 +4728,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4812,7 +4814,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4898,7 +4900,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4984,7 +4986,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5070,7 +5072,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5156,7 +5158,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5242,7 +5244,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5328,7 +5330,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5414,7 +5416,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5500,7 +5502,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5586,7 +5588,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>58</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5672,7 +5674,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>59</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5758,7 +5760,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>60</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5844,7 +5846,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>61</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5930,7 +5932,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>62</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6016,7 +6018,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>63</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6102,7 +6104,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>66</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6188,7 +6190,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>67</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6274,7 +6276,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>68</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6360,7 +6362,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>69</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6446,7 +6448,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>70</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6532,7 +6534,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>73</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6618,7 +6620,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>74</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6704,7 +6706,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>75</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6790,7 +6792,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>76</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6876,7 +6878,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>77</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6962,7 +6964,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>80</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7048,7 +7050,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>81</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7134,7 +7136,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>82</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7220,7 +7222,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>83</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7306,7 +7308,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>84</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7392,7 +7394,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>85</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7478,7 +7480,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>88</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7564,7 +7566,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>89</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7650,7 +7652,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>90</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7736,7 +7738,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>91</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7822,7 +7824,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>94</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7908,7 +7910,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>95</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7994,7 +7996,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>96</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8080,7 +8082,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>97</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8166,7 +8168,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>98</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8252,7 +8254,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8338,7 +8340,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>102</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8424,7 +8426,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>103</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8510,7 +8512,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>104</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8596,7 +8598,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>105</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8682,7 +8684,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>106</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8768,7 +8770,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>107</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8854,7 +8856,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>108</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8940,7 +8942,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>111</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9026,7 +9028,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>112</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9112,7 +9114,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>113</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9198,7 +9200,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>114</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9284,7 +9286,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>115</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9370,7 +9372,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>116</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9456,7 +9458,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>117</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9542,7 +9544,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>787400</xdr:colOff>
           <xdr:row>120</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9820,4560 +9822,4562 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AK129"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="60.36328125" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="1"/>
+    <col min="2" max="2" width="60.36328125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="12.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
     </row>
-    <row r="4" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
     </row>
-    <row r="13" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="P15" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q15" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="T15" s="3" t="s">
+      <c r="T15" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="U15" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="V15" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
     </row>
-    <row r="17" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
     </row>
-    <row r="18" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
+    <row r="18" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
     </row>
-    <row r="19" spans="2:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
     </row>
-    <row r="20" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
     </row>
-    <row r="21" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
     </row>
-    <row r="22" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
     </row>
-    <row r="23" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="L23" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
     </row>
-    <row r="24" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
     </row>
-    <row r="25" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
     </row>
-    <row r="26" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
+    <row r="26" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
     </row>
-    <row r="27" spans="2:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
     </row>
-    <row r="28" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="K28" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="L28" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="M28" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
     </row>
-    <row r="29" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
     </row>
-    <row r="30" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
     </row>
-    <row r="31" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K31" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="L31" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="3"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
     </row>
-    <row r="32" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
     </row>
-    <row r="33" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B33" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K33" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="L33" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
     </row>
-    <row r="34" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
     </row>
-    <row r="35" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="K35" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="L35" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="M35" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="N35" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
     </row>
-    <row r="36" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3"/>
+    <row r="36" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
     </row>
-    <row r="37" spans="2:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
     </row>
-    <row r="38" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
+    <row r="38" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
     </row>
-    <row r="39" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="3" t="s">
+    <row r="39" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B39" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
     </row>
-    <row r="40" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B40" s="3" t="s">
+    <row r="40" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
     </row>
-    <row r="41" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
+    <row r="41" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B41" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
     </row>
-    <row r="42" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="3" t="s">
+    <row r="42" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
     </row>
-    <row r="43" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="3" t="s">
+    <row r="43" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B43" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="3"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
     </row>
-    <row r="44" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="3" t="s">
+    <row r="44" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B44" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
     </row>
-    <row r="45" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="3" t="s">
+    <row r="45" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B45" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="3"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
     </row>
-    <row r="46" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="3" t="s">
+    <row r="46" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B46" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
     </row>
-    <row r="47" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="3" t="s">
+    <row r="47" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
     </row>
-    <row r="48" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="3" t="s">
+    <row r="48" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B48" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
     </row>
-    <row r="49" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="3"/>
+    <row r="49" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
     </row>
-    <row r="50" spans="2:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B50" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
     </row>
-    <row r="51" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
+    <row r="51" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B51" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
     </row>
-    <row r="52" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
+    <row r="52" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B52" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
     </row>
-    <row r="53" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
+    <row r="53" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B53" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="3"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
     </row>
-    <row r="54" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B54" s="3" t="s">
+    <row r="54" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B54" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="3"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
     </row>
-    <row r="55" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="3"/>
-      <c r="AA55" s="3"/>
+    <row r="55" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
     </row>
-    <row r="56" spans="2:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B56" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="3"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="3"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
     </row>
-    <row r="57" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B57" s="3" t="s">
+    <row r="57" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B57" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
     </row>
-    <row r="58" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B58" s="3" t="s">
+    <row r="58" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B58" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
-      <c r="R58" s="3"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="3"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
     </row>
-    <row r="59" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B59" s="3" t="s">
+    <row r="59" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B59" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
     </row>
-    <row r="60" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B60" s="3" t="s">
+    <row r="60" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B60" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
     </row>
-    <row r="61" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="3" t="s">
+    <row r="61" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B61" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="3"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="3"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
     </row>
-    <row r="62" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="3" t="s">
+    <row r="62" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B62" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
     </row>
-    <row r="63" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="3" t="s">
+    <row r="63" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B63" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
     </row>
-    <row r="64" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
+    <row r="64" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
     </row>
-    <row r="65" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="s">
+    <row r="65" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
     </row>
-    <row r="66" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B66" s="3" t="s">
+    <row r="66" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B66" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="3"/>
-      <c r="S66" s="3"/>
-      <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
     </row>
-    <row r="67" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B67" s="3" t="s">
+    <row r="67" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B67" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-      <c r="AA67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
     </row>
-    <row r="68" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B68" s="3" t="s">
+    <row r="68" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B68" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="3"/>
-      <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="3"/>
-      <c r="AA68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
     </row>
-    <row r="69" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B69" s="3" t="s">
+    <row r="69" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B69" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-      <c r="AA69" s="3"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
     </row>
-    <row r="70" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B70" s="3" t="s">
+    <row r="70" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B70" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
     </row>
-    <row r="71" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="3"/>
-      <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
-      <c r="AA71" s="3"/>
+    <row r="71" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
     </row>
-    <row r="72" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="B72" s="2" t="s">
+    <row r="72" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B72" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="3"/>
-      <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
-      <c r="U72" s="3"/>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="3"/>
-      <c r="AA72" s="3"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="4"/>
     </row>
-    <row r="73" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="3" t="s">
+    <row r="73" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B73" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="H73" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="I73" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="3"/>
-      <c r="AA73" s="3"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+      <c r="T73" s="4"/>
+      <c r="U73" s="4"/>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="4"/>
     </row>
-    <row r="74" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
+    <row r="74" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B74" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="H74" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="3"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="3"/>
-      <c r="AA74" s="3"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
     </row>
-    <row r="75" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B75" s="3" t="s">
+    <row r="75" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B75" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="H75" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="3"/>
-      <c r="AA75" s="3"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
     </row>
-    <row r="76" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B76" s="3" t="s">
+    <row r="76" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B76" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="3"/>
-      <c r="S76" s="3"/>
-      <c r="T76" s="3"/>
-      <c r="U76" s="3"/>
-      <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="3"/>
-      <c r="AA76" s="3"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
     </row>
-    <row r="77" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B77" s="3" t="s">
+    <row r="77" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B77" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="3"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="3"/>
-      <c r="AA77" s="3"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
     </row>
-    <row r="78" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-      <c r="Q78" s="3"/>
-      <c r="R78" s="3"/>
-      <c r="S78" s="3"/>
-      <c r="T78" s="3"/>
-      <c r="U78" s="3"/>
-      <c r="V78" s="3"/>
-      <c r="W78" s="3"/>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="3"/>
-      <c r="AA78" s="3"/>
+    <row r="78" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
     </row>
-    <row r="79" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="s">
+    <row r="79" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="3"/>
-      <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
-      <c r="U79" s="3"/>
-      <c r="V79" s="3"/>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="3"/>
-      <c r="AA79" s="3"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="4"/>
     </row>
-    <row r="80" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B80" s="3" t="s">
+    <row r="80" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B80" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3"/>
-      <c r="O80" s="3"/>
-      <c r="P80" s="3"/>
-      <c r="Q80" s="3"/>
-      <c r="R80" s="3"/>
-      <c r="S80" s="3"/>
-      <c r="T80" s="3"/>
-      <c r="U80" s="3"/>
-      <c r="V80" s="3"/>
-      <c r="W80" s="3"/>
-      <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
-      <c r="Z80" s="3"/>
-      <c r="AA80" s="3"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+      <c r="S80" s="4"/>
+      <c r="T80" s="4"/>
+      <c r="U80" s="4"/>
+      <c r="V80" s="4"/>
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="4"/>
     </row>
-    <row r="81" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B81" s="3" t="s">
+    <row r="81" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B81" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="K81" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="L81" s="3"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3"/>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-      <c r="Q81" s="3"/>
-      <c r="R81" s="3"/>
-      <c r="S81" s="3"/>
-      <c r="T81" s="3"/>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="3"/>
-      <c r="AA81" s="3"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+      <c r="S81" s="4"/>
+      <c r="T81" s="4"/>
+      <c r="U81" s="4"/>
+      <c r="V81" s="4"/>
+      <c r="W81" s="4"/>
+      <c r="X81" s="4"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="4"/>
     </row>
-    <row r="82" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B82" s="3" t="s">
+    <row r="82" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B82" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3"/>
-      <c r="M82" s="3"/>
-      <c r="N82" s="3"/>
-      <c r="O82" s="3"/>
-      <c r="P82" s="3"/>
-      <c r="Q82" s="3"/>
-      <c r="R82" s="3"/>
-      <c r="S82" s="3"/>
-      <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="3"/>
-      <c r="AA82" s="3"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4"/>
+      <c r="S82" s="4"/>
+      <c r="T82" s="4"/>
+      <c r="U82" s="4"/>
+      <c r="V82" s="4"/>
+      <c r="W82" s="4"/>
+      <c r="X82" s="4"/>
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="4"/>
+      <c r="AA82" s="4"/>
     </row>
-    <row r="83" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B83" s="3" t="s">
+    <row r="83" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B83" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3"/>
-      <c r="O83" s="3"/>
-      <c r="P83" s="3"/>
-      <c r="Q83" s="3"/>
-      <c r="R83" s="3"/>
-      <c r="S83" s="3"/>
-      <c r="T83" s="3"/>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="3"/>
-      <c r="AA83" s="3"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
+      <c r="T83" s="4"/>
+      <c r="U83" s="4"/>
+      <c r="V83" s="4"/>
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="4"/>
     </row>
-    <row r="84" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B84" s="3" t="s">
+    <row r="84" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B84" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="3"/>
-      <c r="O84" s="3"/>
-      <c r="P84" s="3"/>
-      <c r="Q84" s="3"/>
-      <c r="R84" s="3"/>
-      <c r="S84" s="3"/>
-      <c r="T84" s="3"/>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="3"/>
-      <c r="AA84" s="3"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4"/>
+      <c r="S84" s="4"/>
+      <c r="T84" s="4"/>
+      <c r="U84" s="4"/>
+      <c r="V84" s="4"/>
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+      <c r="AA84" s="4"/>
     </row>
-    <row r="85" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B85" s="3" t="s">
+    <row r="85" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3"/>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3"/>
-      <c r="Q85" s="3"/>
-      <c r="R85" s="3"/>
-      <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="3"/>
-      <c r="AA85" s="3"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="4"/>
+      <c r="S85" s="4"/>
+      <c r="T85" s="4"/>
+      <c r="U85" s="4"/>
+      <c r="V85" s="4"/>
+      <c r="W85" s="4"/>
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="4"/>
     </row>
-    <row r="86" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-      <c r="N86" s="3"/>
-      <c r="O86" s="3"/>
-      <c r="P86" s="3"/>
-      <c r="Q86" s="3"/>
-      <c r="R86" s="3"/>
-      <c r="S86" s="3"/>
-      <c r="T86" s="3"/>
-      <c r="U86" s="3"/>
-      <c r="V86" s="3"/>
-      <c r="W86" s="3"/>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
-      <c r="Z86" s="3"/>
-      <c r="AA86" s="3"/>
+    <row r="86" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4"/>
+      <c r="S86" s="4"/>
+      <c r="T86" s="4"/>
+      <c r="U86" s="4"/>
+      <c r="V86" s="4"/>
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
+      <c r="AA86" s="4"/>
     </row>
-    <row r="87" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A87" s="10" t="s">
+    <row r="87" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3"/>
-      <c r="O87" s="3"/>
-      <c r="P87" s="3"/>
-      <c r="Q87" s="3"/>
-      <c r="R87" s="3"/>
-      <c r="S87" s="3"/>
-      <c r="T87" s="3"/>
-      <c r="U87" s="3"/>
-      <c r="V87" s="3"/>
-      <c r="W87" s="3"/>
-      <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
-      <c r="Z87" s="3"/>
-      <c r="AA87" s="3"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4"/>
+      <c r="S87" s="4"/>
+      <c r="T87" s="4"/>
+      <c r="U87" s="4"/>
+      <c r="V87" s="4"/>
+      <c r="W87" s="4"/>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
+      <c r="AA87" s="4"/>
     </row>
-    <row r="88" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B88" s="3" t="s">
+    <row r="88" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B88" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3"/>
-      <c r="O88" s="3"/>
-      <c r="P88" s="3"/>
-      <c r="Q88" s="3"/>
-      <c r="R88" s="3"/>
-      <c r="S88" s="3"/>
-      <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
-      <c r="V88" s="3"/>
-      <c r="W88" s="3"/>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="3"/>
-      <c r="AA88" s="3"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+      <c r="S88" s="4"/>
+      <c r="T88" s="4"/>
+      <c r="U88" s="4"/>
+      <c r="V88" s="4"/>
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+      <c r="AA88" s="4"/>
     </row>
-    <row r="89" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B89" s="3" t="s">
+    <row r="89" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B89" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
-      <c r="Q89" s="3"/>
-      <c r="R89" s="3"/>
-      <c r="S89" s="3"/>
-      <c r="T89" s="3"/>
-      <c r="U89" s="3"/>
-      <c r="V89" s="3"/>
-      <c r="W89" s="3"/>
-      <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="3"/>
-      <c r="AA89" s="3"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="4"/>
+      <c r="S89" s="4"/>
+      <c r="T89" s="4"/>
+      <c r="U89" s="4"/>
+      <c r="V89" s="4"/>
+      <c r="W89" s="4"/>
+      <c r="X89" s="4"/>
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="4"/>
+      <c r="AA89" s="4"/>
     </row>
-    <row r="90" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B90" s="3" t="s">
+    <row r="90" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B90" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3"/>
-      <c r="O90" s="3"/>
-      <c r="P90" s="3"/>
-      <c r="Q90" s="3"/>
-      <c r="R90" s="3"/>
-      <c r="S90" s="3"/>
-      <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="3"/>
-      <c r="AA90" s="3"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4"/>
+      <c r="S90" s="4"/>
+      <c r="T90" s="4"/>
+      <c r="U90" s="4"/>
+      <c r="V90" s="4"/>
+      <c r="W90" s="4"/>
+      <c r="X90" s="4"/>
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="4"/>
+      <c r="AA90" s="4"/>
     </row>
-    <row r="91" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B91" s="3" t="s">
+    <row r="91" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B91" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3"/>
-      <c r="O91" s="3"/>
-      <c r="P91" s="3"/>
-      <c r="Q91" s="3"/>
-      <c r="R91" s="3"/>
-      <c r="S91" s="3"/>
-      <c r="T91" s="3"/>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="3"/>
-      <c r="AA91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4"/>
+      <c r="S91" s="4"/>
+      <c r="T91" s="4"/>
+      <c r="U91" s="4"/>
+      <c r="V91" s="4"/>
+      <c r="W91" s="4"/>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="4"/>
     </row>
-    <row r="92" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-      <c r="N92" s="3"/>
-      <c r="O92" s="3"/>
-      <c r="P92" s="3"/>
-      <c r="Q92" s="3"/>
-      <c r="R92" s="3"/>
-      <c r="S92" s="3"/>
-      <c r="T92" s="3"/>
-      <c r="U92" s="3"/>
-      <c r="V92" s="3"/>
-      <c r="W92" s="3"/>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="3"/>
-      <c r="AA92" s="3"/>
+    <row r="92" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+      <c r="S92" s="4"/>
+      <c r="T92" s="4"/>
+      <c r="U92" s="4"/>
+      <c r="V92" s="4"/>
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="4"/>
     </row>
-    <row r="93" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
+    <row r="93" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
-      <c r="M93" s="3"/>
-      <c r="N93" s="3"/>
-      <c r="O93" s="3"/>
-      <c r="P93" s="3"/>
-      <c r="Q93" s="3"/>
-      <c r="R93" s="3"/>
-      <c r="S93" s="3"/>
-      <c r="T93" s="3"/>
-      <c r="U93" s="3"/>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
-      <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
-      <c r="Z93" s="3"/>
-      <c r="AA93" s="3"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="4"/>
+      <c r="S93" s="4"/>
+      <c r="T93" s="4"/>
+      <c r="U93" s="4"/>
+      <c r="V93" s="4"/>
+      <c r="W93" s="4"/>
+      <c r="X93" s="4"/>
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="4"/>
+      <c r="AA93" s="4"/>
     </row>
-    <row r="94" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B94" s="3" t="s">
+    <row r="94" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B94" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H94" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-      <c r="N94" s="3"/>
-      <c r="O94" s="3"/>
-      <c r="P94" s="3"/>
-      <c r="Q94" s="3"/>
-      <c r="R94" s="3"/>
-      <c r="S94" s="3"/>
-      <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="3"/>
-      <c r="AA94" s="3"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+      <c r="S94" s="4"/>
+      <c r="T94" s="4"/>
+      <c r="U94" s="4"/>
+      <c r="V94" s="4"/>
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="4"/>
     </row>
-    <row r="95" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B95" s="3" t="s">
+    <row r="95" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B95" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3"/>
-      <c r="O95" s="3"/>
-      <c r="P95" s="3"/>
-      <c r="Q95" s="3"/>
-      <c r="R95" s="3"/>
-      <c r="S95" s="3"/>
-      <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="3"/>
-      <c r="AA95" s="3"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="4"/>
+      <c r="T95" s="4"/>
+      <c r="U95" s="4"/>
+      <c r="V95" s="4"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
     </row>
-    <row r="96" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B96" s="3" t="s">
+    <row r="96" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B96" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="3"/>
-      <c r="O96" s="3"/>
-      <c r="P96" s="3"/>
-      <c r="Q96" s="3"/>
-      <c r="R96" s="3"/>
-      <c r="S96" s="3"/>
-      <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="3"/>
-      <c r="AA96" s="3"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+      <c r="S96" s="4"/>
+      <c r="T96" s="4"/>
+      <c r="U96" s="4"/>
+      <c r="V96" s="4"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
     </row>
-    <row r="97" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B97" s="3" t="s">
+    <row r="97" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B97" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3"/>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3"/>
-      <c r="Q97" s="3"/>
-      <c r="R97" s="3"/>
-      <c r="S97" s="3"/>
-      <c r="T97" s="3"/>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="3"/>
-      <c r="AA97" s="3"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="4"/>
+      <c r="S97" s="4"/>
+      <c r="T97" s="4"/>
+      <c r="U97" s="4"/>
+      <c r="V97" s="4"/>
+      <c r="W97" s="4"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="4"/>
     </row>
-    <row r="98" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B98" s="3" t="s">
+    <row r="98" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B98" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="G98" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3"/>
-      <c r="O98" s="3"/>
-      <c r="P98" s="3"/>
-      <c r="Q98" s="3"/>
-      <c r="R98" s="3"/>
-      <c r="S98" s="3"/>
-      <c r="T98" s="3"/>
-      <c r="U98" s="3"/>
-      <c r="V98" s="3"/>
-      <c r="W98" s="3"/>
-      <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
-      <c r="Z98" s="3"/>
-      <c r="AA98" s="3"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="4"/>
+      <c r="S98" s="4"/>
+      <c r="T98" s="4"/>
+      <c r="U98" s="4"/>
+      <c r="V98" s="4"/>
+      <c r="W98" s="4"/>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="4"/>
+      <c r="AA98" s="4"/>
     </row>
-    <row r="99" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
-      <c r="N99" s="3"/>
-      <c r="O99" s="3"/>
-      <c r="P99" s="3"/>
-      <c r="Q99" s="3"/>
-      <c r="R99" s="3"/>
-      <c r="S99" s="3"/>
-      <c r="T99" s="3"/>
-      <c r="U99" s="3"/>
-      <c r="V99" s="3"/>
-      <c r="W99" s="3"/>
-      <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
-      <c r="Z99" s="3"/>
-      <c r="AA99" s="3"/>
+    <row r="99" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="4"/>
+      <c r="S99" s="4"/>
+      <c r="T99" s="4"/>
+      <c r="U99" s="4"/>
+      <c r="V99" s="4"/>
+      <c r="W99" s="4"/>
+      <c r="X99" s="4"/>
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="4"/>
+      <c r="AA99" s="4"/>
     </row>
-    <row r="100" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
+    <row r="100" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-      <c r="M100" s="3"/>
-      <c r="N100" s="3"/>
-      <c r="O100" s="3"/>
-      <c r="P100" s="3"/>
-      <c r="Q100" s="3"/>
-      <c r="R100" s="3"/>
-      <c r="S100" s="3"/>
-      <c r="T100" s="3"/>
-      <c r="U100" s="3"/>
-      <c r="V100" s="3"/>
-      <c r="W100" s="3"/>
-      <c r="X100" s="3"/>
-      <c r="Y100" s="3"/>
-      <c r="Z100" s="3"/>
-      <c r="AA100" s="3"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="4"/>
+      <c r="T100" s="4"/>
+      <c r="U100" s="4"/>
+      <c r="V100" s="4"/>
+      <c r="W100" s="4"/>
+      <c r="X100" s="4"/>
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="4"/>
+      <c r="AA100" s="4"/>
     </row>
-    <row r="101" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B101" s="3" t="s">
+    <row r="101" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B101" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
-      <c r="N101" s="3"/>
-      <c r="O101" s="3"/>
-      <c r="P101" s="3"/>
-      <c r="Q101" s="3"/>
-      <c r="R101" s="3"/>
-      <c r="S101" s="3"/>
-      <c r="T101" s="3"/>
-      <c r="U101" s="3"/>
-      <c r="V101" s="3"/>
-      <c r="W101" s="3"/>
-      <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
-      <c r="Z101" s="3"/>
-      <c r="AA101" s="3"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4"/>
+      <c r="S101" s="4"/>
+      <c r="T101" s="4"/>
+      <c r="U101" s="4"/>
+      <c r="V101" s="4"/>
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="4"/>
     </row>
-    <row r="102" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B102" s="3" t="s">
+    <row r="102" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B102" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
-      <c r="N102" s="3"/>
-      <c r="O102" s="3"/>
-      <c r="P102" s="3"/>
-      <c r="Q102" s="3"/>
-      <c r="R102" s="3"/>
-      <c r="S102" s="3"/>
-      <c r="T102" s="3"/>
-      <c r="U102" s="3"/>
-      <c r="V102" s="3"/>
-      <c r="W102" s="3"/>
-      <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
-      <c r="Z102" s="3"/>
-      <c r="AA102" s="3"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+      <c r="T102" s="4"/>
+      <c r="U102" s="4"/>
+      <c r="V102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
     </row>
-    <row r="103" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B103" s="3" t="s">
+    <row r="103" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B103" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3"/>
-      <c r="O103" s="3"/>
-      <c r="P103" s="3"/>
-      <c r="Q103" s="3"/>
-      <c r="R103" s="3"/>
-      <c r="S103" s="3"/>
-      <c r="T103" s="3"/>
-      <c r="U103" s="3"/>
-      <c r="V103" s="3"/>
-      <c r="W103" s="3"/>
-      <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
-      <c r="Z103" s="3"/>
-      <c r="AA103" s="3"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+      <c r="T103" s="4"/>
+      <c r="U103" s="4"/>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
     </row>
-    <row r="104" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B104" s="3" t="s">
+    <row r="104" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B104" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3"/>
-      <c r="M104" s="3"/>
-      <c r="N104" s="3"/>
-      <c r="O104" s="3"/>
-      <c r="P104" s="3"/>
-      <c r="Q104" s="3"/>
-      <c r="R104" s="3"/>
-      <c r="S104" s="3"/>
-      <c r="T104" s="3"/>
-      <c r="U104" s="3"/>
-      <c r="V104" s="3"/>
-      <c r="W104" s="3"/>
-      <c r="X104" s="3"/>
-      <c r="Y104" s="3"/>
-      <c r="Z104" s="3"/>
-      <c r="AA104" s="3"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="4"/>
+      <c r="T104" s="4"/>
+      <c r="U104" s="4"/>
+      <c r="V104" s="4"/>
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+      <c r="AA104" s="4"/>
     </row>
-    <row r="105" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="3" t="s">
+    <row r="105" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B105" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
-      <c r="L105" s="3"/>
-      <c r="M105" s="3"/>
-      <c r="N105" s="3"/>
-      <c r="O105" s="3"/>
-      <c r="P105" s="3"/>
-      <c r="Q105" s="3"/>
-      <c r="R105" s="3"/>
-      <c r="S105" s="3"/>
-      <c r="T105" s="3"/>
-      <c r="U105" s="3"/>
-      <c r="V105" s="3"/>
-      <c r="W105" s="3"/>
-      <c r="X105" s="3"/>
-      <c r="Y105" s="3"/>
-      <c r="Z105" s="3"/>
-      <c r="AA105" s="3"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+      <c r="S105" s="4"/>
+      <c r="T105" s="4"/>
+      <c r="U105" s="4"/>
+      <c r="V105" s="4"/>
+      <c r="W105" s="4"/>
+      <c r="X105" s="4"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="4"/>
+      <c r="AA105" s="4"/>
     </row>
-    <row r="106" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B106" s="3" t="s">
+    <row r="106" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B106" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
-      <c r="L106" s="3"/>
-      <c r="M106" s="3"/>
-      <c r="N106" s="3"/>
-      <c r="O106" s="3"/>
-      <c r="P106" s="3"/>
-      <c r="Q106" s="3"/>
-      <c r="R106" s="3"/>
-      <c r="S106" s="3"/>
-      <c r="T106" s="3"/>
-      <c r="U106" s="3"/>
-      <c r="V106" s="3"/>
-      <c r="W106" s="3"/>
-      <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
-      <c r="Z106" s="3"/>
-      <c r="AA106" s="3"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
+      <c r="T106" s="4"/>
+      <c r="U106" s="4"/>
+      <c r="V106" s="4"/>
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="4"/>
+      <c r="Z106" s="4"/>
+      <c r="AA106" s="4"/>
     </row>
-    <row r="107" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B107" s="3" t="s">
+    <row r="107" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B107" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="G107" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3"/>
-      <c r="J107" s="3"/>
-      <c r="K107" s="3"/>
-      <c r="L107" s="3"/>
-      <c r="M107" s="3"/>
-      <c r="N107" s="3"/>
-      <c r="O107" s="3"/>
-      <c r="P107" s="3"/>
-      <c r="Q107" s="3"/>
-      <c r="R107" s="3"/>
-      <c r="S107" s="3"/>
-      <c r="T107" s="3"/>
-      <c r="U107" s="3"/>
-      <c r="V107" s="3"/>
-      <c r="W107" s="3"/>
-      <c r="X107" s="3"/>
-      <c r="Y107" s="3"/>
-      <c r="Z107" s="3"/>
-      <c r="AA107" s="3"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+      <c r="U107" s="4"/>
+      <c r="V107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
     </row>
-    <row r="108" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B108" s="3" t="s">
+    <row r="108" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B108" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3"/>
-      <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
-      <c r="L108" s="3"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="3"/>
-      <c r="O108" s="3"/>
-      <c r="P108" s="3"/>
-      <c r="Q108" s="3"/>
-      <c r="R108" s="3"/>
-      <c r="S108" s="3"/>
-      <c r="T108" s="3"/>
-      <c r="U108" s="3"/>
-      <c r="V108" s="3"/>
-      <c r="W108" s="3"/>
-      <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
-      <c r="Z108" s="3"/>
-      <c r="AA108" s="3"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+      <c r="U108" s="4"/>
+      <c r="V108" s="4"/>
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
+      <c r="AA108" s="4"/>
     </row>
-    <row r="109" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-      <c r="O109" s="3"/>
-      <c r="P109" s="3"/>
-      <c r="Q109" s="3"/>
-      <c r="R109" s="3"/>
-      <c r="S109" s="3"/>
-      <c r="T109" s="3"/>
-      <c r="U109" s="3"/>
-      <c r="V109" s="3"/>
-      <c r="W109" s="3"/>
-      <c r="X109" s="3"/>
-      <c r="Y109" s="3"/>
-      <c r="Z109" s="3"/>
-      <c r="AA109" s="3"/>
+    <row r="109" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+      <c r="U109" s="4"/>
+      <c r="V109" s="4"/>
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
     </row>
-    <row r="110" spans="1:27" ht="13" x14ac:dyDescent="0.3">
-      <c r="A110" s="10" t="s">
+    <row r="110" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
-      <c r="O110" s="3"/>
-      <c r="P110" s="3"/>
-      <c r="Q110" s="3"/>
-      <c r="R110" s="3"/>
-      <c r="S110" s="3"/>
-      <c r="T110" s="3"/>
-      <c r="U110" s="3"/>
-      <c r="V110" s="3"/>
-      <c r="W110" s="3"/>
-      <c r="X110" s="3"/>
-      <c r="Y110" s="3"/>
-      <c r="Z110" s="3"/>
-      <c r="AA110" s="3"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="4"/>
+      <c r="T110" s="4"/>
+      <c r="U110" s="4"/>
+      <c r="V110" s="4"/>
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="4"/>
+      <c r="AA110" s="4"/>
     </row>
-    <row r="111" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B111" s="3" t="s">
+    <row r="111" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B111" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3"/>
-      <c r="O111" s="3"/>
-      <c r="P111" s="3"/>
-      <c r="Q111" s="3"/>
-      <c r="R111" s="3"/>
-      <c r="S111" s="3"/>
-      <c r="T111" s="3"/>
-      <c r="U111" s="3"/>
-      <c r="V111" s="3"/>
-      <c r="W111" s="3"/>
-      <c r="X111" s="3"/>
-      <c r="Y111" s="3"/>
-      <c r="Z111" s="3"/>
-      <c r="AA111" s="3"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="4"/>
+      <c r="T111" s="4"/>
+      <c r="U111" s="4"/>
+      <c r="V111" s="4"/>
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+      <c r="AA111" s="4"/>
     </row>
-    <row r="112" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B112" s="3" t="s">
+    <row r="112" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B112" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="3"/>
-      <c r="O112" s="3"/>
-      <c r="P112" s="3"/>
-      <c r="Q112" s="3"/>
-      <c r="R112" s="3"/>
-      <c r="S112" s="3"/>
-      <c r="T112" s="3"/>
-      <c r="U112" s="3"/>
-      <c r="V112" s="3"/>
-      <c r="W112" s="3"/>
-      <c r="X112" s="3"/>
-      <c r="Y112" s="3"/>
-      <c r="Z112" s="3"/>
-      <c r="AA112" s="3"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4"/>
+      <c r="S112" s="4"/>
+      <c r="T112" s="4"/>
+      <c r="U112" s="4"/>
+      <c r="V112" s="4"/>
+      <c r="W112" s="4"/>
+      <c r="X112" s="4"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="4"/>
+      <c r="AA112" s="4"/>
     </row>
-    <row r="113" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B113" s="3" t="s">
+    <row r="113" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B113" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3"/>
-      <c r="O113" s="3"/>
-      <c r="P113" s="3"/>
-      <c r="Q113" s="3"/>
-      <c r="R113" s="3"/>
-      <c r="S113" s="3"/>
-      <c r="T113" s="3"/>
-      <c r="U113" s="3"/>
-      <c r="V113" s="3"/>
-      <c r="W113" s="3"/>
-      <c r="X113" s="3"/>
-      <c r="Y113" s="3"/>
-      <c r="Z113" s="3"/>
-      <c r="AA113" s="3"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="4"/>
+      <c r="T113" s="4"/>
+      <c r="U113" s="4"/>
+      <c r="V113" s="4"/>
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="4"/>
+      <c r="AA113" s="4"/>
     </row>
-    <row r="114" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B114" s="3" t="s">
+    <row r="114" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B114" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="3"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="3"/>
-      <c r="O114" s="3"/>
-      <c r="P114" s="3"/>
-      <c r="Q114" s="3"/>
-      <c r="R114" s="3"/>
-      <c r="S114" s="3"/>
-      <c r="T114" s="3"/>
-      <c r="U114" s="3"/>
-      <c r="V114" s="3"/>
-      <c r="W114" s="3"/>
-      <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
-      <c r="Z114" s="3"/>
-      <c r="AA114" s="3"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="4"/>
+      <c r="T114" s="4"/>
+      <c r="U114" s="4"/>
+      <c r="V114" s="4"/>
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
+      <c r="AA114" s="4"/>
     </row>
-    <row r="115" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B115" s="3" t="s">
+    <row r="115" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B115" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3"/>
-      <c r="O115" s="3"/>
-      <c r="P115" s="3"/>
-      <c r="Q115" s="3"/>
-      <c r="R115" s="3"/>
-      <c r="S115" s="3"/>
-      <c r="T115" s="3"/>
-      <c r="U115" s="3"/>
-      <c r="V115" s="3"/>
-      <c r="W115" s="3"/>
-      <c r="X115" s="3"/>
-      <c r="Y115" s="3"/>
-      <c r="Z115" s="3"/>
-      <c r="AA115" s="3"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+      <c r="T115" s="4"/>
+      <c r="U115" s="4"/>
+      <c r="V115" s="4"/>
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+      <c r="AA115" s="4"/>
     </row>
-    <row r="116" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B116" s="9" t="s">
+    <row r="116" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B116" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C116" s="9" t="s">
+      <c r="C116" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="D116" s="9" t="s">
+      <c r="D116" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="E116" s="9" t="s">
+      <c r="E116" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="F116" s="9" t="s">
+      <c r="F116" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="G116" s="9" t="s">
+      <c r="G116" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="H116" s="9"/>
-      <c r="I116" s="9"/>
-      <c r="J116" s="9"/>
-      <c r="K116" s="7" t="s">
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="3"/>
-      <c r="O116" s="3"/>
-      <c r="P116" s="3"/>
-      <c r="Q116" s="3"/>
-      <c r="R116" s="3"/>
-      <c r="S116" s="3"/>
-      <c r="T116" s="3"/>
-      <c r="U116" s="3"/>
-      <c r="V116" s="3"/>
-      <c r="W116" s="3"/>
-      <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
-      <c r="Z116" s="3"/>
-      <c r="AA116" s="3"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="4"/>
+      <c r="T116" s="4"/>
+      <c r="U116" s="4"/>
+      <c r="V116" s="4"/>
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="4"/>
+      <c r="AA116" s="4"/>
     </row>
-    <row r="117" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B117" s="3" t="s">
+    <row r="117" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B117" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="3"/>
-      <c r="M117" s="3"/>
-      <c r="N117" s="3"/>
-      <c r="O117" s="3"/>
-      <c r="P117" s="3"/>
-      <c r="Q117" s="3"/>
-      <c r="R117" s="3"/>
-      <c r="S117" s="3"/>
-      <c r="T117" s="3"/>
-      <c r="U117" s="3"/>
-      <c r="V117" s="3"/>
-      <c r="W117" s="3"/>
-      <c r="X117" s="3"/>
-      <c r="Y117" s="3"/>
-      <c r="Z117" s="3"/>
-      <c r="AA117" s="3"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="4"/>
+      <c r="S117" s="4"/>
+      <c r="T117" s="4"/>
+      <c r="U117" s="4"/>
+      <c r="V117" s="4"/>
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="4"/>
+      <c r="AA117" s="4"/>
     </row>
-    <row r="118" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
-      <c r="O118" s="3"/>
-      <c r="P118" s="3"/>
-      <c r="Q118" s="3"/>
-      <c r="R118" s="3"/>
-      <c r="S118" s="3"/>
-      <c r="T118" s="3"/>
-      <c r="U118" s="3"/>
-      <c r="V118" s="3"/>
-      <c r="W118" s="3"/>
-      <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
-      <c r="Z118" s="3"/>
-      <c r="AA118" s="3"/>
+    <row r="118" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="4"/>
+      <c r="T118" s="4"/>
+      <c r="U118" s="4"/>
+      <c r="V118" s="4"/>
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
+      <c r="AA118" s="4"/>
     </row>
-    <row r="119" spans="1:37" ht="13" x14ac:dyDescent="0.3">
-      <c r="A119" s="8" t="s">
+    <row r="119" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
-      <c r="O119" s="3"/>
-      <c r="P119" s="3"/>
-      <c r="Q119" s="3"/>
-      <c r="R119" s="3"/>
-      <c r="S119" s="3"/>
-      <c r="T119" s="3"/>
-      <c r="U119" s="3"/>
-      <c r="V119" s="3"/>
-      <c r="W119" s="3"/>
-      <c r="X119" s="3"/>
-      <c r="Y119" s="3"/>
-      <c r="Z119" s="3"/>
-      <c r="AA119" s="3"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="4"/>
+      <c r="T119" s="4"/>
+      <c r="U119" s="4"/>
+      <c r="V119" s="4"/>
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+      <c r="AA119" s="4"/>
     </row>
-    <row r="120" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B120" s="3" t="s">
+    <row r="120" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B120" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="E120" s="3" t="s">
+      <c r="E120" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G120" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="H120" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="I120" s="3" t="s">
+      <c r="I120" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="J120" s="3" t="s">
+      <c r="J120" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="K120" s="3" t="s">
+      <c r="K120" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="L120" s="3" t="s">
+      <c r="L120" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="M120" s="3" t="s">
+      <c r="M120" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="N120" s="3" t="s">
+      <c r="N120" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="O120" s="3" t="s">
+      <c r="O120" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="P120" s="3" t="s">
+      <c r="P120" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="Q120" s="3" t="s">
+      <c r="Q120" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="R120" s="3" t="s">
+      <c r="R120" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="S120" s="3" t="s">
+      <c r="S120" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="T120" s="3" t="s">
+      <c r="T120" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="U120" s="3" t="s">
+      <c r="U120" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="V120" s="3" t="s">
+      <c r="V120" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="W120" s="3" t="s">
+      <c r="W120" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="X120" s="3" t="s">
+      <c r="X120" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="Y120" s="3" t="s">
+      <c r="Y120" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="Z120" s="3" t="s">
+      <c r="Z120" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="AA120" s="3" t="s">
+      <c r="AA120" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="AB120" t="s">
+      <c r="AB120" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="AC120" t="s">
+      <c r="AC120" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="AD120" t="s">
+      <c r="AD120" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="AE120" t="s">
+      <c r="AE120" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="AF120" t="s">
+      <c r="AF120" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="AG120" t="s">
+      <c r="AG120" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="AH120" t="s">
+      <c r="AH120" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="AI120" t="s">
+      <c r="AI120" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="AJ120" t="s">
+      <c r="AJ120" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="AK120" t="s">
+      <c r="AK120" s="1" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="121" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="3"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3"/>
-      <c r="L121" s="3"/>
-      <c r="M121" s="3"/>
-      <c r="N121" s="3"/>
-      <c r="O121" s="3"/>
-      <c r="P121" s="3"/>
-      <c r="Q121" s="3"/>
-      <c r="R121" s="3"/>
-      <c r="S121" s="3"/>
-      <c r="T121" s="3"/>
-      <c r="U121" s="3"/>
-      <c r="V121" s="3"/>
-      <c r="W121" s="3"/>
-      <c r="X121" s="3"/>
-      <c r="Y121" s="3"/>
-      <c r="Z121" s="3"/>
-      <c r="AA121" s="3"/>
+    <row r="121" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4"/>
+      <c r="S121" s="4"/>
+      <c r="T121" s="4"/>
+      <c r="U121" s="4"/>
+      <c r="V121" s="4"/>
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="4"/>
+      <c r="AA121" s="4"/>
     </row>
-    <row r="122" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="3"/>
-      <c r="J122" s="3"/>
-      <c r="K122" s="3"/>
-      <c r="L122" s="3"/>
-      <c r="M122" s="3"/>
-      <c r="N122" s="3"/>
-      <c r="O122" s="3"/>
-      <c r="P122" s="3"/>
-      <c r="Q122" s="3"/>
-      <c r="R122" s="3"/>
-      <c r="S122" s="3"/>
-      <c r="T122" s="3"/>
-      <c r="U122" s="3"/>
-      <c r="V122" s="3"/>
-      <c r="W122" s="3"/>
-      <c r="X122" s="3"/>
-      <c r="Y122" s="3"/>
-      <c r="Z122" s="3"/>
-      <c r="AA122" s="3"/>
+    <row r="122" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="4"/>
+      <c r="R122" s="4"/>
+      <c r="S122" s="4"/>
+      <c r="T122" s="4"/>
+      <c r="U122" s="4"/>
+      <c r="V122" s="4"/>
+      <c r="W122" s="4"/>
+      <c r="X122" s="4"/>
+      <c r="Y122" s="4"/>
+      <c r="Z122" s="4"/>
+      <c r="AA122" s="4"/>
     </row>
-    <row r="123" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="3"/>
-      <c r="J123" s="3"/>
-      <c r="K123" s="3"/>
-      <c r="L123" s="3"/>
-      <c r="M123" s="3"/>
-      <c r="N123" s="3"/>
-      <c r="O123" s="3"/>
-      <c r="P123" s="3"/>
-      <c r="Q123" s="3"/>
-      <c r="R123" s="3"/>
-      <c r="S123" s="3"/>
-      <c r="T123" s="3"/>
-      <c r="U123" s="3"/>
-      <c r="V123" s="3"/>
-      <c r="W123" s="3"/>
-      <c r="X123" s="3"/>
-      <c r="Y123" s="3"/>
-      <c r="Z123" s="3"/>
-      <c r="AA123" s="3"/>
+    <row r="123" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B123" s="4"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4"/>
+      <c r="S123" s="4"/>
+      <c r="T123" s="4"/>
+      <c r="U123" s="4"/>
+      <c r="V123" s="4"/>
+      <c r="W123" s="4"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="4"/>
+      <c r="AA123" s="4"/>
     </row>
-    <row r="124" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
-      <c r="I124" s="3"/>
-      <c r="J124" s="3"/>
-      <c r="K124" s="3"/>
-      <c r="L124" s="3"/>
-      <c r="M124" s="3"/>
-      <c r="N124" s="3"/>
-      <c r="O124" s="3"/>
-      <c r="P124" s="3"/>
-      <c r="Q124" s="3"/>
-      <c r="R124" s="3"/>
-      <c r="S124" s="3"/>
-      <c r="T124" s="3"/>
-      <c r="U124" s="3"/>
-      <c r="V124" s="3"/>
-      <c r="W124" s="3"/>
-      <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
-      <c r="Z124" s="3"/>
-      <c r="AA124" s="3"/>
+    <row r="124" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B124" s="4"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4"/>
+      <c r="S124" s="4"/>
+      <c r="T124" s="4"/>
+      <c r="U124" s="4"/>
+      <c r="V124" s="4"/>
+      <c r="W124" s="4"/>
+      <c r="X124" s="4"/>
+      <c r="Y124" s="4"/>
+      <c r="Z124" s="4"/>
+      <c r="AA124" s="4"/>
     </row>
-    <row r="125" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
-      <c r="I125" s="3"/>
-      <c r="J125" s="3"/>
-      <c r="K125" s="3"/>
-      <c r="L125" s="3"/>
-      <c r="M125" s="3"/>
-      <c r="N125" s="3"/>
-      <c r="O125" s="3"/>
-      <c r="P125" s="3"/>
-      <c r="Q125" s="3"/>
-      <c r="R125" s="3"/>
-      <c r="S125" s="3"/>
-      <c r="T125" s="3"/>
-      <c r="U125" s="3"/>
-      <c r="V125" s="3"/>
-      <c r="W125" s="3"/>
-      <c r="X125" s="3"/>
-      <c r="Y125" s="3"/>
-      <c r="Z125" s="3"/>
-      <c r="AA125" s="3"/>
+    <row r="125" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B125" s="4"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4"/>
+      <c r="N125" s="4"/>
+      <c r="O125" s="4"/>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="4"/>
+      <c r="R125" s="4"/>
+      <c r="S125" s="4"/>
+      <c r="T125" s="4"/>
+      <c r="U125" s="4"/>
+      <c r="V125" s="4"/>
+      <c r="W125" s="4"/>
+      <c r="X125" s="4"/>
+      <c r="Y125" s="4"/>
+      <c r="Z125" s="4"/>
+      <c r="AA125" s="4"/>
     </row>
-    <row r="126" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="3"/>
-      <c r="J126" s="3"/>
-      <c r="K126" s="3"/>
-      <c r="L126" s="3"/>
-      <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
-      <c r="O126" s="3"/>
-      <c r="P126" s="3"/>
-      <c r="Q126" s="3"/>
-      <c r="R126" s="3"/>
-      <c r="S126" s="3"/>
-      <c r="T126" s="3"/>
-      <c r="U126" s="3"/>
-      <c r="V126" s="3"/>
-      <c r="W126" s="3"/>
-      <c r="X126" s="3"/>
-      <c r="Y126" s="3"/>
-      <c r="Z126" s="3"/>
-      <c r="AA126" s="3"/>
+    <row r="126" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B126" s="4"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4"/>
+      <c r="N126" s="4"/>
+      <c r="O126" s="4"/>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="4"/>
+      <c r="R126" s="4"/>
+      <c r="S126" s="4"/>
+      <c r="T126" s="4"/>
+      <c r="U126" s="4"/>
+      <c r="V126" s="4"/>
+      <c r="W126" s="4"/>
+      <c r="X126" s="4"/>
+      <c r="Y126" s="4"/>
+      <c r="Z126" s="4"/>
+      <c r="AA126" s="4"/>
     </row>
-    <row r="127" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
-      <c r="I127" s="3"/>
-      <c r="J127" s="3"/>
-      <c r="K127" s="3"/>
-      <c r="L127" s="3"/>
-      <c r="M127" s="3"/>
-      <c r="N127" s="3"/>
-      <c r="O127" s="3"/>
-      <c r="P127" s="3"/>
-      <c r="Q127" s="3"/>
-      <c r="R127" s="3"/>
-      <c r="S127" s="3"/>
-      <c r="T127" s="3"/>
-      <c r="U127" s="3"/>
-      <c r="V127" s="3"/>
-      <c r="W127" s="3"/>
-      <c r="X127" s="3"/>
-      <c r="Y127" s="3"/>
-      <c r="Z127" s="3"/>
-      <c r="AA127" s="3"/>
+    <row r="127" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B127" s="4"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+      <c r="L127" s="4"/>
+      <c r="M127" s="4"/>
+      <c r="N127" s="4"/>
+      <c r="O127" s="4"/>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="4"/>
+      <c r="R127" s="4"/>
+      <c r="S127" s="4"/>
+      <c r="T127" s="4"/>
+      <c r="U127" s="4"/>
+      <c r="V127" s="4"/>
+      <c r="W127" s="4"/>
+      <c r="X127" s="4"/>
+      <c r="Y127" s="4"/>
+      <c r="Z127" s="4"/>
+      <c r="AA127" s="4"/>
     </row>
-    <row r="128" spans="1:37" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="3"/>
-      <c r="J128" s="3"/>
-      <c r="K128" s="3"/>
-      <c r="L128" s="3"/>
-      <c r="M128" s="3"/>
-      <c r="N128" s="3"/>
-      <c r="O128" s="3"/>
-      <c r="P128" s="3"/>
-      <c r="Q128" s="3"/>
-      <c r="R128" s="3"/>
-      <c r="S128" s="3"/>
-      <c r="T128" s="3"/>
-      <c r="U128" s="3"/>
-      <c r="V128" s="3"/>
-      <c r="W128" s="3"/>
-      <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
-      <c r="Z128" s="3"/>
-      <c r="AA128" s="3"/>
+    <row r="128" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B128" s="4"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
+      <c r="L128" s="4"/>
+      <c r="M128" s="4"/>
+      <c r="N128" s="4"/>
+      <c r="O128" s="4"/>
+      <c r="P128" s="4"/>
+      <c r="Q128" s="4"/>
+      <c r="R128" s="4"/>
+      <c r="S128" s="4"/>
+      <c r="T128" s="4"/>
+      <c r="U128" s="4"/>
+      <c r="V128" s="4"/>
+      <c r="W128" s="4"/>
+      <c r="X128" s="4"/>
+      <c r="Y128" s="4"/>
+      <c r="Z128" s="4"/>
+      <c r="AA128" s="4"/>
     </row>
-    <row r="129" spans="2:27" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="3"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="3"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
-      <c r="O129" s="3"/>
-      <c r="P129" s="3"/>
-      <c r="Q129" s="3"/>
-      <c r="R129" s="3"/>
-      <c r="S129" s="3"/>
-      <c r="T129" s="3"/>
-      <c r="U129" s="3"/>
-      <c r="V129" s="3"/>
-      <c r="W129" s="3"/>
-      <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
-      <c r="Z129" s="3"/>
-      <c r="AA129" s="3"/>
+    <row r="129" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B129" s="4"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
+      <c r="R129" s="4"/>
+      <c r="S129" s="4"/>
+      <c r="T129" s="4"/>
+      <c r="U129" s="4"/>
+      <c r="V129" s="4"/>
+      <c r="W129" s="4"/>
+      <c r="X129" s="4"/>
+      <c r="Y129" s="4"/>
+      <c r="Z129" s="4"/>
+      <c r="AA129" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -14638,7 +14642,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>19</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14704,7 +14708,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>22</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14726,7 +14730,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>23</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14748,7 +14752,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>24</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14770,7 +14774,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>25</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14792,7 +14796,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>28</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14814,7 +14818,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>29</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14836,7 +14840,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>30</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14858,7 +14862,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>31</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14880,7 +14884,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>32</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14902,7 +14906,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>33</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14924,7 +14928,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>34</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14946,7 +14950,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14968,7 +14972,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>38</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -14990,7 +14994,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>39</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15012,7 +15016,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>40</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15034,7 +15038,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>41</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15056,7 +15060,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>42</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15078,7 +15082,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>43</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15100,7 +15104,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>44</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15122,7 +15126,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>45</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15144,7 +15148,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>46</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15166,7 +15170,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>47</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15188,7 +15192,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>48</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15210,7 +15214,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>51</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15232,7 +15236,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>52</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15254,7 +15258,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>53</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15276,7 +15280,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>54</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15298,7 +15302,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>57</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15320,7 +15324,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>58</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15342,7 +15346,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>59</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15364,7 +15368,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>60</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15386,7 +15390,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>61</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15408,7 +15412,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>62</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15430,7 +15434,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>63</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15452,7 +15456,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>66</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15474,7 +15478,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>67</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15496,7 +15500,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>68</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15518,7 +15522,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>69</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15540,7 +15544,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>70</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15562,7 +15566,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>73</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15584,7 +15588,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>74</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15606,7 +15610,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>75</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15628,7 +15632,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>76</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15650,7 +15654,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>77</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15672,7 +15676,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>80</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15694,7 +15698,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>81</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15716,7 +15720,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>82</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15738,7 +15742,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>83</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15760,7 +15764,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>84</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15782,7 +15786,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>85</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15804,7 +15808,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>88</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15826,7 +15830,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>89</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15848,7 +15852,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>90</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15870,7 +15874,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>91</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15892,7 +15896,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>94</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15914,7 +15918,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>95</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15936,7 +15940,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>96</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15958,7 +15962,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>97</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15980,7 +15984,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>98</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16002,7 +16006,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>101</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16024,7 +16028,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>102</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16046,7 +16050,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>103</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16068,7 +16072,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>104</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16090,7 +16094,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>105</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16112,7 +16116,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>106</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16134,7 +16138,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>107</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16156,7 +16160,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>108</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16178,7 +16182,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>111</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16200,7 +16204,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>112</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16222,7 +16226,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>113</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16244,7 +16248,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>114</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16266,7 +16270,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>115</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16288,7 +16292,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>116</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16310,7 +16314,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>117</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16332,7 +16336,7 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>787400</xdr:colOff>
                     <xdr:row>120</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
+                    <xdr:rowOff>31750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>

--- a/LeetCode Patterns.xlsx
+++ b/LeetCode Patterns.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sksat\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\placements\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D56097D-CF3B-45CB-863E-0205535D4F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31987ECD-CA1A-4507-8483-617A423B3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="477">
   <si>
     <t xml:space="preserve">Author : Taufique </t>
   </si>
@@ -1459,6 +1459,9 @@
   </si>
   <si>
     <t>COMP</t>
+  </si>
+  <si>
+    <t>striver</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1588,6 +1591,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10204,6 +10208,9 @@
       <c r="AA12" s="4"/>
     </row>
     <row r="13" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>476</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>

--- a/LeetCode Patterns.xlsx
+++ b/LeetCode Patterns.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\placements\practice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sksat\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31987ECD-CA1A-4507-8483-617A423B3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF86CD30-F669-4A6F-9CD7-DB98B52FB6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,14 +31,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="478">
   <si>
     <t xml:space="preserve">Author : Taufique </t>
   </si>
   <si>
-    <t>Pattern</t>
-  </si>
-  <si>
     <t>Problems</t>
   </si>
   <si>
@@ -1446,9 +1443,6 @@
     <t>43. Multiply Strings</t>
   </si>
   <si>
-    <t>needed</t>
-  </si>
-  <si>
     <t>comp</t>
   </si>
   <si>
@@ -1462,13 +1456,22 @@
   </si>
   <si>
     <t>striver</t>
+  </si>
+  <si>
+    <t>17 prblms</t>
+  </si>
+  <si>
+    <t>22  prblms</t>
+  </si>
+  <si>
+    <t>don’t touch</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1528,6 +1531,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1579,7 +1595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1591,7 +1607,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1622,27 +1639,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1686,7 +1703,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1710,11 +1727,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1730,15 +1747,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1778,7 +1795,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1802,7 +1819,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1838,7 +1855,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1954,10 +1971,6 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp88.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp89.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2851,92 +2864,6 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-IN" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Check Box 1</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>44450</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>12700</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>787400</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>31750</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1037" name="Check Box 13" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1037"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9839,11 +9766,9 @@
       </c>
     </row>
     <row r="3" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -9872,10 +9797,10 @@
     </row>
     <row r="4" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -9905,40 +9830,40 @@
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="M5" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -9957,16 +9882,16 @@
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -9993,16 +9918,16 @@
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -10029,34 +9954,34 @@
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -10077,10 +10002,10 @@
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -10109,13 +10034,13 @@
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -10143,19 +10068,19 @@
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -10209,10 +10134,10 @@
     </row>
     <row r="13" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -10242,22 +10167,22 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>163</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -10282,67 +10207,67 @@
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="L15" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="M15" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="N15" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="O15" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="P15" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="R15" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="S15" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="S15" s="4" t="s">
+      <c r="T15" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="T15" s="4" t="s">
+      <c r="U15" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="U15" s="4" t="s">
+      <c r="V15" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="V15" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -10352,16 +10277,16 @@
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -10388,13 +10313,13 @@
     </row>
     <row r="17" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -10450,7 +10375,7 @@
     </row>
     <row r="19" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -10480,22 +10405,22 @@
     </row>
     <row r="20" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -10520,32 +10445,32 @@
     </row>
     <row r="21" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -10564,25 +10489,25 @@
     </row>
     <row r="22" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -10606,42 +10531,42 @@
     </row>
     <row r="23" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="J23" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="K23" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="L23" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
@@ -10656,13 +10581,13 @@
     </row>
     <row r="24" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -10690,16 +10615,16 @@
     </row>
     <row r="25" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -10754,7 +10679,7 @@
     </row>
     <row r="27" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -10784,40 +10709,40 @@
     </row>
     <row r="28" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="J28" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="K28" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="L28" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="M28" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
@@ -10836,19 +10761,19 @@
     </row>
     <row r="29" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -10874,19 +10799,19 @@
     </row>
     <row r="30" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B30" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -10912,37 +10837,37 @@
     </row>
     <row r="31" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="E31" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="I31" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="J31" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="K31" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="L31" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
@@ -10962,10 +10887,10 @@
     </row>
     <row r="32" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -10994,37 +10919,37 @@
     </row>
     <row r="33" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="I33" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="J33" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="K33" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="L33" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -11044,10 +10969,10 @@
     </row>
     <row r="34" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -11076,43 +11001,43 @@
     </row>
     <row r="35" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="I35" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="J35" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="K35" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="L35" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="M35" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="M35" s="4" t="s">
+      <c r="N35" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
@@ -11158,7 +11083,7 @@
     </row>
     <row r="37" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -11188,31 +11113,31 @@
     </row>
     <row r="38" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="G38" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H38" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="J38" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -11234,10 +11159,10 @@
     </row>
     <row r="39" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B39" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -11266,16 +11191,16 @@
     </row>
     <row r="40" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B40" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -11302,13 +11227,13 @@
     </row>
     <row r="41" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -11336,13 +11261,13 @@
     </row>
     <row r="42" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -11370,13 +11295,13 @@
     </row>
     <row r="43" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -11404,10 +11329,10 @@
     </row>
     <row r="44" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -11436,28 +11361,28 @@
     </row>
     <row r="45" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B45" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
@@ -11480,13 +11405,13 @@
     </row>
     <row r="46" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B46" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -11514,16 +11439,16 @@
     </row>
     <row r="47" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B47" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -11550,19 +11475,19 @@
     </row>
     <row r="48" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B48" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -11586,7 +11511,7 @@
       <c r="Z48" s="4"/>
       <c r="AA48" s="4"/>
     </row>
-    <row r="49" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -11614,9 +11539,12 @@
       <c r="Z49" s="4"/>
       <c r="AA49" s="4"/>
     </row>
-    <row r="50" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>476</v>
+      </c>
       <c r="B50" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -11644,33 +11572,33 @@
       <c r="Z50" s="4"/>
       <c r="AA50" s="4"/>
     </row>
-    <row r="51" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B51" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="F51" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="I51" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="J51" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -11690,19 +11618,21 @@
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
     </row>
-    <row r="52" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B52" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -11724,21 +11654,21 @@
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
     </row>
-    <row r="53" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B53" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -11762,33 +11692,33 @@
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
     </row>
-    <row r="54" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B54" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="J54" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
@@ -11808,7 +11738,7 @@
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>
     </row>
-    <row r="55" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -11836,9 +11766,12 @@
       <c r="Z55" s="4"/>
       <c r="AA55" s="4"/>
     </row>
-    <row r="56" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="B56" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -11866,21 +11799,21 @@
       <c r="Z56" s="4"/>
       <c r="AA56" s="4"/>
     </row>
-    <row r="57" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B57" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C57" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="F57" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -11904,18 +11837,18 @@
       <c r="Z57" s="4"/>
       <c r="AA57" s="4"/>
     </row>
-    <row r="58" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B58" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C58" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -11940,15 +11873,15 @@
       <c r="Z58" s="4"/>
       <c r="AA58" s="4"/>
     </row>
-    <row r="59" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B59" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -11974,15 +11907,15 @@
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
     </row>
-    <row r="60" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B60" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -12008,18 +11941,18 @@
       <c r="Z60" s="4"/>
       <c r="AA60" s="4"/>
     </row>
-    <row r="61" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B61" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C61" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -12044,15 +11977,15 @@
       <c r="Z61" s="4"/>
       <c r="AA61" s="4"/>
     </row>
-    <row r="62" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B62" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -12078,12 +12011,12 @@
       <c r="Z62" s="4"/>
       <c r="AA62" s="4"/>
     </row>
-    <row r="63" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B63" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -12110,7 +12043,7 @@
       <c r="Z63" s="4"/>
       <c r="AA63" s="4"/>
     </row>
-    <row r="64" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -12140,10 +12073,10 @@
     </row>
     <row r="65" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -12173,22 +12106,22 @@
     </row>
     <row r="66" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B66" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="F66" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -12213,13 +12146,13 @@
     </row>
     <row r="67" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B67" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -12247,13 +12180,13 @@
     </row>
     <row r="68" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B68" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C68" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -12281,10 +12214,10 @@
     </row>
     <row r="69" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B69" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -12313,10 +12246,10 @@
     </row>
     <row r="70" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B70" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -12373,7 +12306,7 @@
     </row>
     <row r="72" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B72" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -12403,31 +12336,31 @@
     </row>
     <row r="73" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B73" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C73" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="E73" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="F73" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="G73" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="H73" s="4" t="s">
+      <c r="I73" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="I73" s="4" t="s">
+      <c r="J73" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
@@ -12449,25 +12382,25 @@
     </row>
     <row r="74" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B74" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="E74" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
@@ -12491,31 +12424,31 @@
     </row>
     <row r="75" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B75" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="F75" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="G75" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="H75" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="I75" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="I75" s="4" t="s">
+      <c r="J75" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
@@ -12537,13 +12470,13 @@
     </row>
     <row r="76" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B76" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C76" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
@@ -12571,10 +12504,10 @@
     </row>
     <row r="77" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B77" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -12630,11 +12563,11 @@
       <c r="AA78" s="4"/>
     </row>
     <row r="79" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
-        <v>471</v>
+      <c r="A79" s="11" t="s">
+        <v>474</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -12664,22 +12597,22 @@
     </row>
     <row r="80" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B80" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="G80" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>378</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -12704,34 +12637,34 @@
     </row>
     <row r="81" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B81" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C81" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="F81" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="H81" s="10" t="s">
+      <c r="I81" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="I81" s="4" t="s">
+      <c r="J81" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="J81" s="4" t="s">
+      <c r="K81" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="K81" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -12752,19 +12685,19 @@
     </row>
     <row r="82" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B82" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C82" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="F82" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -12790,16 +12723,16 @@
     </row>
     <row r="83" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B83" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C83" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
@@ -12826,10 +12759,10 @@
     </row>
     <row r="84" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B84" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -12858,13 +12791,13 @@
     </row>
     <row r="85" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B85" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C85" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
@@ -12920,10 +12853,10 @@
     </row>
     <row r="87" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -12953,19 +12886,19 @@
     </row>
     <row r="88" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B88" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C88" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="E88" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="F88" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -12991,10 +12924,10 @@
     </row>
     <row r="89" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B89" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -13023,10 +12956,10 @@
     </row>
     <row r="90" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B90" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -13055,13 +12988,13 @@
     </row>
     <row r="91" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B91" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
@@ -13117,10 +13050,10 @@
     </row>
     <row r="93" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -13150,25 +13083,25 @@
     </row>
     <row r="94" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B94" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C94" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="E94" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="F94" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="G94" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
@@ -13192,10 +13125,10 @@
     </row>
     <row r="95" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B95" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -13224,13 +13157,13 @@
     </row>
     <row r="96" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B96" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C96" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
@@ -13258,10 +13191,10 @@
     </row>
     <row r="97" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B97" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -13290,22 +13223,22 @@
     </row>
     <row r="98" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B98" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C98" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="F98" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="G98" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -13358,10 +13291,10 @@
     </row>
     <row r="100" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -13391,13 +13324,13 @@
     </row>
     <row r="101" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B101" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C101" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
@@ -13425,16 +13358,16 @@
     </row>
     <row r="102" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B102" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="E102" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
@@ -13461,10 +13394,10 @@
     </row>
     <row r="103" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B103" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -13493,10 +13426,10 @@
     </row>
     <row r="104" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B104" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -13525,10 +13458,10 @@
     </row>
     <row r="105" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B105" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -13557,10 +13490,10 @@
     </row>
     <row r="106" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B106" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C106" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -13589,22 +13522,22 @@
     </row>
     <row r="107" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B107" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C107" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F107" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F107" s="4" t="s">
+      <c r="G107" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -13629,10 +13562,10 @@
     </row>
     <row r="108" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B108" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -13689,10 +13622,10 @@
     </row>
     <row r="110" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -13722,16 +13655,16 @@
     </row>
     <row r="111" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B111" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C111" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="E111" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -13758,13 +13691,13 @@
     </row>
     <row r="112" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B112" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C112" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>428</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
@@ -13792,10 +13725,10 @@
     </row>
     <row r="113" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B113" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C113" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -13824,10 +13757,10 @@
     </row>
     <row r="114" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B114" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -13856,10 +13789,10 @@
     </row>
     <row r="115" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B115" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -13888,28 +13821,28 @@
     </row>
     <row r="116" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B116" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C116" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="D116" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="D116" s="8" t="s">
+      <c r="E116" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="E116" s="8" t="s">
+      <c r="F116" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="F116" s="8" t="s">
+      <c r="G116" s="8" t="s">
         <v>432</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>433</v>
       </c>
       <c r="H116" s="8"/>
       <c r="I116" s="8"/>
       <c r="J116" s="8"/>
       <c r="K116" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -13930,10 +13863,10 @@
     </row>
     <row r="117" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B117" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -13990,10 +13923,10 @@
     </row>
     <row r="119" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -14023,112 +13956,112 @@
     </row>
     <row r="120" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B120" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C120" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="E120" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="F120" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="G120" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="H120" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H120" s="4" t="s">
+      <c r="I120" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="I120" s="4" t="s">
+      <c r="J120" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="J120" s="4" t="s">
+      <c r="K120" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="K120" s="4" t="s">
+      <c r="L120" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="L120" s="4" t="s">
+      <c r="M120" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="M120" s="4" t="s">
+      <c r="N120" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="N120" s="4" t="s">
+      <c r="O120" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="O120" s="4" t="s">
+      <c r="P120" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="P120" s="4" t="s">
+      <c r="Q120" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="Q120" s="4" t="s">
+      <c r="R120" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="R120" s="4" t="s">
+      <c r="S120" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="S120" s="4" t="s">
+      <c r="T120" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="T120" s="4" t="s">
+      <c r="U120" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="U120" s="4" t="s">
+      <c r="V120" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="V120" s="4" t="s">
+      <c r="W120" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="W120" s="4" t="s">
+      <c r="X120" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="X120" s="4" t="s">
+      <c r="Y120" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="Y120" s="4" t="s">
+      <c r="Z120" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="Z120" s="4" t="s">
+      <c r="AA120" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="AA120" s="4" t="s">
+      <c r="AB120" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="AB120" s="1" t="s">
+      <c r="AC120" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="AC120" s="1" t="s">
+      <c r="AD120" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="AD120" s="1" t="s">
+      <c r="AE120" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="AE120" s="1" t="s">
+      <c r="AF120" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="AF120" s="1" t="s">
+      <c r="AG120" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="AG120" s="1" t="s">
+      <c r="AH120" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="AH120" s="1" t="s">
+      <c r="AI120" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="AI120" s="1" t="s">
+      <c r="AJ120" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="AJ120" s="1" t="s">
+      <c r="AK120" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="AK120" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="121" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
@@ -14636,29 +14569,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1037" r:id="rId15" name="Check Box 13">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>44450</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>787400</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>31750</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1038" r:id="rId16" name="Check Box 14">
+            <control shapeId="1038" r:id="rId15" name="Check Box 14">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14680,7 +14591,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1039" r:id="rId17" name="Check Box 15">
+            <control shapeId="1039" r:id="rId16" name="Check Box 15">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14702,7 +14613,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1040" r:id="rId18" name="Check Box 16">
+            <control shapeId="1040" r:id="rId17" name="Check Box 16">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14724,7 +14635,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1041" r:id="rId19" name="Check Box 17">
+            <control shapeId="1041" r:id="rId18" name="Check Box 17">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14746,7 +14657,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1042" r:id="rId20" name="Check Box 18">
+            <control shapeId="1042" r:id="rId19" name="Check Box 18">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14768,7 +14679,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1043" r:id="rId21" name="Check Box 19">
+            <control shapeId="1043" r:id="rId20" name="Check Box 19">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14790,7 +14701,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId22" name="Check Box 21">
+            <control shapeId="1045" r:id="rId21" name="Check Box 21">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14812,7 +14723,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId23" name="Check Box 22">
+            <control shapeId="1046" r:id="rId22" name="Check Box 22">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14834,7 +14745,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId24" name="Check Box 23">
+            <control shapeId="1047" r:id="rId23" name="Check Box 23">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14856,7 +14767,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId25" name="Check Box 24">
+            <control shapeId="1048" r:id="rId24" name="Check Box 24">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14878,7 +14789,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId26" name="Check Box 25">
+            <control shapeId="1049" r:id="rId25" name="Check Box 25">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14900,7 +14811,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId27" name="Check Box 26">
+            <control shapeId="1050" r:id="rId26" name="Check Box 26">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14922,7 +14833,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId28" name="Check Box 27">
+            <control shapeId="1051" r:id="rId27" name="Check Box 27">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14944,7 +14855,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId29" name="Check Box 28">
+            <control shapeId="1052" r:id="rId28" name="Check Box 28">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14966,7 +14877,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId30" name="Check Box 30">
+            <control shapeId="1054" r:id="rId29" name="Check Box 30">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14988,7 +14899,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId31" name="Check Box 31">
+            <control shapeId="1055" r:id="rId30" name="Check Box 31">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15010,7 +14921,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId32" name="Check Box 32">
+            <control shapeId="1056" r:id="rId31" name="Check Box 32">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15032,7 +14943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId33" name="Check Box 33">
+            <control shapeId="1057" r:id="rId32" name="Check Box 33">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15054,7 +14965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId34" name="Check Box 34">
+            <control shapeId="1058" r:id="rId33" name="Check Box 34">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15076,7 +14987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId35" name="Check Box 35">
+            <control shapeId="1059" r:id="rId34" name="Check Box 35">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15098,7 +15009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId36" name="Check Box 36">
+            <control shapeId="1060" r:id="rId35" name="Check Box 36">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15120,7 +15031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId37" name="Check Box 37">
+            <control shapeId="1061" r:id="rId36" name="Check Box 37">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15142,7 +15053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId38" name="Check Box 38">
+            <control shapeId="1062" r:id="rId37" name="Check Box 38">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15164,7 +15075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId39" name="Check Box 39">
+            <control shapeId="1063" r:id="rId38" name="Check Box 39">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15186,7 +15097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId40" name="Check Box 40">
+            <control shapeId="1064" r:id="rId39" name="Check Box 40">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15208,7 +15119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId41" name="Check Box 42">
+            <control shapeId="1066" r:id="rId40" name="Check Box 42">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15230,7 +15141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId42" name="Check Box 43">
+            <control shapeId="1067" r:id="rId41" name="Check Box 43">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15252,7 +15163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId43" name="Check Box 44">
+            <control shapeId="1068" r:id="rId42" name="Check Box 44">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15274,7 +15185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId44" name="Check Box 45">
+            <control shapeId="1069" r:id="rId43" name="Check Box 45">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15296,7 +15207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId45" name="Check Box 47">
+            <control shapeId="1071" r:id="rId44" name="Check Box 47">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15318,7 +15229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId46" name="Check Box 48">
+            <control shapeId="1072" r:id="rId45" name="Check Box 48">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15340,7 +15251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId47" name="Check Box 49">
+            <control shapeId="1073" r:id="rId46" name="Check Box 49">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15362,7 +15273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId48" name="Check Box 50">
+            <control shapeId="1074" r:id="rId47" name="Check Box 50">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15384,7 +15295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId49" name="Check Box 51">
+            <control shapeId="1075" r:id="rId48" name="Check Box 51">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15406,7 +15317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId50" name="Check Box 52">
+            <control shapeId="1076" r:id="rId49" name="Check Box 52">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15428,7 +15339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId51" name="Check Box 53">
+            <control shapeId="1077" r:id="rId50" name="Check Box 53">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15450,7 +15361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId52" name="Check Box 55">
+            <control shapeId="1079" r:id="rId51" name="Check Box 55">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15472,7 +15383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId53" name="Check Box 56">
+            <control shapeId="1080" r:id="rId52" name="Check Box 56">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15494,7 +15405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId54" name="Check Box 57">
+            <control shapeId="1081" r:id="rId53" name="Check Box 57">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15516,7 +15427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId55" name="Check Box 58">
+            <control shapeId="1082" r:id="rId54" name="Check Box 58">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15538,7 +15449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId56" name="Check Box 59">
+            <control shapeId="1083" r:id="rId55" name="Check Box 59">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15560,7 +15471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId57" name="Check Box 61">
+            <control shapeId="1085" r:id="rId56" name="Check Box 61">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15582,7 +15493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId58" name="Check Box 62">
+            <control shapeId="1086" r:id="rId57" name="Check Box 62">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15604,7 +15515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId59" name="Check Box 63">
+            <control shapeId="1087" r:id="rId58" name="Check Box 63">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15626,7 +15537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId60" name="Check Box 64">
+            <control shapeId="1088" r:id="rId59" name="Check Box 64">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15648,7 +15559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId61" name="Check Box 65">
+            <control shapeId="1089" r:id="rId60" name="Check Box 65">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15670,7 +15581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId62" name="Check Box 67">
+            <control shapeId="1091" r:id="rId61" name="Check Box 67">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15692,7 +15603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId63" name="Check Box 68">
+            <control shapeId="1092" r:id="rId62" name="Check Box 68">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15714,7 +15625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId64" name="Check Box 69">
+            <control shapeId="1093" r:id="rId63" name="Check Box 69">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15736,7 +15647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId65" name="Check Box 70">
+            <control shapeId="1094" r:id="rId64" name="Check Box 70">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15758,7 +15669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId66" name="Check Box 71">
+            <control shapeId="1095" r:id="rId65" name="Check Box 71">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15780,7 +15691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId67" name="Check Box 72">
+            <control shapeId="1096" r:id="rId66" name="Check Box 72">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15802,7 +15713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId68" name="Check Box 74">
+            <control shapeId="1098" r:id="rId67" name="Check Box 74">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15824,7 +15735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId69" name="Check Box 75">
+            <control shapeId="1099" r:id="rId68" name="Check Box 75">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15846,7 +15757,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId70" name="Check Box 76">
+            <control shapeId="1100" r:id="rId69" name="Check Box 76">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15868,7 +15779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId71" name="Check Box 77">
+            <control shapeId="1101" r:id="rId70" name="Check Box 77">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15890,7 +15801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId72" name="Check Box 79">
+            <control shapeId="1103" r:id="rId71" name="Check Box 79">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15912,7 +15823,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId73" name="Check Box 80">
+            <control shapeId="1104" r:id="rId72" name="Check Box 80">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15934,7 +15845,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId74" name="Check Box 81">
+            <control shapeId="1105" r:id="rId73" name="Check Box 81">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15956,7 +15867,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId75" name="Check Box 82">
+            <control shapeId="1106" r:id="rId74" name="Check Box 82">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15978,7 +15889,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId76" name="Check Box 83">
+            <control shapeId="1107" r:id="rId75" name="Check Box 83">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16000,7 +15911,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId77" name="Check Box 85">
+            <control shapeId="1109" r:id="rId76" name="Check Box 85">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16022,7 +15933,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId78" name="Check Box 86">
+            <control shapeId="1110" r:id="rId77" name="Check Box 86">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16044,7 +15955,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId79" name="Check Box 87">
+            <control shapeId="1111" r:id="rId78" name="Check Box 87">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16066,7 +15977,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId80" name="Check Box 88">
+            <control shapeId="1112" r:id="rId79" name="Check Box 88">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16088,7 +15999,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId81" name="Check Box 89">
+            <control shapeId="1113" r:id="rId80" name="Check Box 89">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16110,7 +16021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId82" name="Check Box 90">
+            <control shapeId="1114" r:id="rId81" name="Check Box 90">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16132,7 +16043,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId83" name="Check Box 91">
+            <control shapeId="1115" r:id="rId82" name="Check Box 91">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16154,7 +16065,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId84" name="Check Box 92">
+            <control shapeId="1116" r:id="rId83" name="Check Box 92">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16176,7 +16087,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId85" name="Check Box 94">
+            <control shapeId="1118" r:id="rId84" name="Check Box 94">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16198,7 +16109,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId86" name="Check Box 95">
+            <control shapeId="1119" r:id="rId85" name="Check Box 95">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16220,7 +16131,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId87" name="Check Box 96">
+            <control shapeId="1120" r:id="rId86" name="Check Box 96">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16242,7 +16153,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId88" name="Check Box 97">
+            <control shapeId="1121" r:id="rId87" name="Check Box 97">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16264,7 +16175,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId89" name="Check Box 98">
+            <control shapeId="1122" r:id="rId88" name="Check Box 98">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16286,7 +16197,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId90" name="Check Box 99">
+            <control shapeId="1123" r:id="rId89" name="Check Box 99">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16308,7 +16219,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId91" name="Check Box 100">
+            <control shapeId="1124" r:id="rId90" name="Check Box 100">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16330,7 +16241,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId92" name="Check Box 102">
+            <control shapeId="1126" r:id="rId91" name="Check Box 102">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/LeetCode Patterns.xlsx
+++ b/LeetCode Patterns.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sksat\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\placements\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF86CD30-F669-4A6F-9CD7-DB98B52FB6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD22FE7-6379-4C8D-B0C7-08BFAE9AAA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="478">
   <si>
     <t xml:space="preserve">Author : Taufique </t>
   </si>
@@ -1461,17 +1461,17 @@
     <t>17 prblms</t>
   </si>
   <si>
-    <t>22  prblms</t>
-  </si>
-  <si>
     <t>don’t touch</t>
+  </si>
+  <si>
+    <t>comp &amp; revised</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1544,6 +1544,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1595,7 +1601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1609,6 +1615,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1763,7 +1770,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1831,11 +1838,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9755,9 +9762,44 @@
   <dimension ref="A1:AK129"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="1"/>
-    <col min="2" max="2" width="60.36328125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="12.6328125" style="1"/>
+    <col min="1" max="1" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="65.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="64.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="54" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="84" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="60.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="51.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="61.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="53.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="61.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="59.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="38.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="72.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="75.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="36.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="38.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="48.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="42.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="30.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="27.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="38.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="12.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
@@ -10311,7 +10353,7 @@
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
     </row>
-    <row r="17" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>15</v>
       </c>
@@ -10345,7 +10387,7 @@
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
     </row>
-    <row r="18" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -10373,7 +10415,10 @@
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
     </row>
-    <row r="19" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>473</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
@@ -10403,7 +10448,7 @@
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
     </row>
-    <row r="20" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
         <v>17</v>
       </c>
@@ -10443,7 +10488,7 @@
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
     </row>
-    <row r="21" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>18</v>
       </c>
@@ -10487,7 +10532,7 @@
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
     </row>
-    <row r="22" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
         <v>19</v>
       </c>
@@ -10529,7 +10574,7 @@
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
     </row>
-    <row r="23" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
@@ -10579,7 +10624,7 @@
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
     </row>
-    <row r="24" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
@@ -10613,7 +10658,7 @@
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
     </row>
-    <row r="25" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>22</v>
       </c>
@@ -10649,7 +10694,7 @@
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
     </row>
-    <row r="26" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -10677,7 +10722,7 @@
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
     </row>
-    <row r="27" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>23</v>
       </c>
@@ -10707,7 +10752,7 @@
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
     </row>
-    <row r="28" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
@@ -10759,7 +10804,7 @@
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
     </row>
-    <row r="29" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
         <v>25</v>
       </c>
@@ -10797,7 +10842,7 @@
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
     </row>
-    <row r="30" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B30" s="4" t="s">
         <v>26</v>
       </c>
@@ -10835,7 +10880,7 @@
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
     </row>
-    <row r="31" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B31" s="4" t="s">
         <v>27</v>
       </c>
@@ -10885,7 +10930,7 @@
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
     </row>
-    <row r="32" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>28</v>
       </c>
@@ -11540,8 +11585,8 @@
       <c r="AA49" s="4"/>
     </row>
     <row r="50" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>476</v>
+      <c r="A50" s="11" t="s">
+        <v>473</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>48</v>
@@ -11631,7 +11676,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -11667,10 +11712,12 @@
       <c r="E53" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="G53" s="4"/>
+      <c r="G53" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -11696,7 +11743,7 @@
       <c r="B54" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="8" t="s">
         <v>316</v>
       </c>
       <c r="D54" s="4" t="s">
@@ -13291,7 +13338,7 @@
     </row>
     <row r="100" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>100</v>
